--- a/data/trans_orig/P1429-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1429-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de osteoporosis en 2007</t>
+          <t>Población con diagnóstico de osteoporosis en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13770</t>
+          <t>13773</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31726</t>
+          <t>31663</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>82000</t>
+          <t>81843</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>119758</t>
+          <t>122214</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>101615</t>
+          <t>102801</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>144528</t>
+          <t>146928</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>999997</t>
+          <t>1000060</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1017953</t>
+          <t>1017950</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1195355</t>
+          <t>1192899</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1233113</t>
+          <t>1233270</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2202307</t>
+          <t>2199907</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2245220</t>
+          <t>2244034</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,62%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4706</t>
+          <t>4916</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18243</t>
+          <t>18095</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27232</t>
+          <t>26521</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50642</t>
+          <t>50687</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34021</t>
+          <t>35171</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63240</t>
+          <t>63087</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1675170</t>
+          <t>1675318</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1688707</t>
+          <t>1688497</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1537031</t>
+          <t>1536986</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1560441</t>
+          <t>1561152</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3217846</t>
+          <t>3217999</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3247065</t>
+          <t>3245915</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>833</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9486</t>
+          <t>9650</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2783</t>
+          <t>2840</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14129</t>
+          <t>13024</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17778</t>
+          <t>18194</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>541922</t>
+          <t>541758</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>550573</t>
+          <t>550575</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>462283</t>
+          <t>463388</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>473629</t>
+          <t>473572</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1010042</t>
+          <t>1009626</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1022492</t>
+          <t>1022602</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,49%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23203</t>
+          <t>24797</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45780</t>
+          <t>48276</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>122035</t>
+          <t>121146</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>169587</t>
+          <t>169092</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>155574</t>
+          <t>153714</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>206337</t>
+          <t>207773</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3230763</t>
+          <t>3228267</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3253340</t>
+          <t>3251746</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3209610</t>
+          <t>3210105</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3257162</t>
+          <t>3258051</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6449404</t>
+          <t>6447968</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6500167</t>
+          <t>6502027</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,69%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de osteoporosis en 2012</t>
+          <t>Población con diagnóstico de osteoporosis en 2012 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14040</t>
+          <t>12110</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>89675</t>
+          <t>91565</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>132231</t>
+          <t>130198</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>93253</t>
+          <t>93070</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>137389</t>
+          <t>135491</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>959600</t>
+          <t>961530</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1204457</t>
+          <t>1206490</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1247013</t>
+          <t>1245123</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2172939</t>
+          <t>2174837</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2217075</t>
+          <t>2217258</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>983</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8154</t>
+          <t>8185</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15421</t>
+          <t>15706</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36473</t>
+          <t>35898</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18928</t>
+          <t>18748</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41343</t>
+          <t>39763</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1955803</t>
+          <t>1955772</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1962967</t>
+          <t>1962974</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1718119</t>
+          <t>1718694</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1739171</t>
+          <t>1738886</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3677206</t>
+          <t>3678786</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3699621</t>
+          <t>3699801</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3097</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17255</t>
+          <t>17185</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3216</t>
+          <t>3719</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17110</t>
+          <t>18119</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>479077</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>481181</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>441376</t>
+          <t>441446</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>455534</t>
+          <t>454966</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>922703</t>
+          <t>921694</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>936597</t>
+          <t>936094</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2088</t>
+          <t>2057</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15104</t>
+          <t>16052</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>120402</t>
+          <t>119193</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>172415</t>
+          <t>169762</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>125804</t>
+          <t>126669</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>175794</t>
+          <t>175391</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3403675</t>
+          <t>3402727</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3416691</t>
+          <t>3416722</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3377496</t>
+          <t>3380149</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3429509</t>
+          <t>3430718</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6792896</t>
+          <t>6793299</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6842886</t>
+          <t>6842021</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,18%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de osteoporosis en 2016</t>
+          <t>Población con diagnóstico de osteoporosis en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1688</t>
+          <t>1695</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11328</t>
+          <t>10545</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>51956</t>
+          <t>53025</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>85815</t>
+          <t>87091</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>53575</t>
+          <t>56151</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>90662</t>
+          <t>89966</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>743019</t>
+          <t>743802</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>752659</t>
+          <t>752652</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>908845</t>
+          <t>907569</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>942704</t>
+          <t>941635</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1658345</t>
+          <t>1659041</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1695432</t>
+          <t>1692856</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,79%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1664</t>
+          <t>1829</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11067</t>
+          <t>10858</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31240</t>
+          <t>32426</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58667</t>
+          <t>60022</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37396</t>
+          <t>35986</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>65769</t>
+          <t>64904</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2065318</t>
+          <t>2065527</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2074721</t>
+          <t>2074556</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>99,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1929633</t>
+          <t>1928278</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1957060</t>
+          <t>1955874</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3998916</t>
+          <t>3999781</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4027289</t>
+          <t>4028699</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7739</t>
+          <t>7342</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5064</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19374</t>
+          <t>18560</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6915</t>
+          <t>6500</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22546</t>
+          <t>23182</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>539147</t>
+          <t>539544</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>529766</t>
+          <t>530580</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>544076</t>
+          <t>543946</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1073481</t>
+          <t>1072845</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1089112</t>
+          <t>1089527</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6111</t>
+          <t>5914</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19784</t>
+          <t>19918</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>100200</t>
+          <t>100033</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>146889</t>
+          <t>144158</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>111624</t>
+          <t>110567</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>161391</t>
+          <t>159455</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3357834</t>
+          <t>3357700</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3371507</t>
+          <t>3371704</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3385211</t>
+          <t>3387942</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3431900</t>
+          <t>3432067</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6748327</t>
+          <t>6750263</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6798094</t>
+          <t>6799151</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de osteoporosis en 2023</t>
+          <t>Población con diagnóstico de osteoporosis en 2023 (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6955</t>
+          <t>6931</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17481</t>
+          <t>16998</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>73509</t>
+          <t>73700</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>98877</t>
+          <t>99230</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>84938</t>
+          <t>84581</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>111221</t>
+          <t>111128</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>492709</t>
+          <t>493192</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>503235</t>
+          <t>503259</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>650036</t>
+          <t>649683</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>675404</t>
+          <t>675213</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1147882</t>
+          <t>1147975</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1174165</t>
+          <t>1174522</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,28%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7845</t>
+          <t>7251</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32701</t>
+          <t>30574</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39926</t>
+          <t>38291</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72078</t>
+          <t>71079</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53438</t>
+          <t>53989</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>90750</t>
+          <t>89961</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2256390</t>
+          <t>2258517</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2281246</t>
+          <t>2281840</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2159492</t>
+          <t>2160491</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2191644</t>
+          <t>2193279</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4429912</t>
+          <t>4430701</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4467224</t>
+          <t>4466673</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>735</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6425</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11963</t>
+          <t>11484</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23476</t>
+          <t>23208</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13386</t>
+          <t>13347</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26686</t>
+          <t>26186</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>639149</t>
+          <t>639041</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>644845</t>
+          <t>644839</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>635401</t>
+          <t>635669</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>646914</t>
+          <t>647393</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1277765</t>
+          <t>1278265</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1291065</t>
+          <t>1291104</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19380</t>
+          <t>19125</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43911</t>
+          <t>46243</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>128160</t>
+          <t>130966</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>181991</t>
+          <t>182774</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>158626</t>
+          <t>159239</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>212939</t>
+          <t>214130</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3400944</t>
+          <t>3398612</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3425475</t>
+          <t>3425730</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,7 +6699,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3457369</t>
+          <t>3456586</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3511200</t>
+          <t>3508394</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6871276</t>
+          <t>6870085</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6925589</t>
+          <t>6924976</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1429-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1429-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13773</t>
+          <t>13157</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31663</t>
+          <t>31785</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>81843</t>
+          <t>83842</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>122214</t>
+          <t>123176</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>102801</t>
+          <t>102379</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>146928</t>
+          <t>145059</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1000060</t>
+          <t>999938</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1017950</t>
+          <t>1018566</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1192899</t>
+          <t>1191937</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1233270</t>
+          <t>1231271</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2199907</t>
+          <t>2201776</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2244034</t>
+          <t>2244456</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,64%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4916</t>
+          <t>4249</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18095</t>
+          <t>18721</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26521</t>
+          <t>26363</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50687</t>
+          <t>51334</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35171</t>
+          <t>35385</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63087</t>
+          <t>63913</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1675318</t>
+          <t>1674692</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1688497</t>
+          <t>1689164</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1536986</t>
+          <t>1536339</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1561152</t>
+          <t>1561310</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3217999</t>
+          <t>3217173</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3245915</t>
+          <t>3245701</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>835</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9650</t>
+          <t>9091</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2840</t>
+          <t>2775</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13024</t>
+          <t>12513</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5218</t>
+          <t>5143</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18194</t>
+          <t>16906</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>541758</t>
+          <t>542317</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>550575</t>
+          <t>550573</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>463388</t>
+          <t>463899</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>473572</t>
+          <t>473637</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1009626</t>
+          <t>1010914</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1022602</t>
+          <t>1022677</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24797</t>
+          <t>24124</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48276</t>
+          <t>46684</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>121146</t>
+          <t>121541</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>169092</t>
+          <t>169876</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>153714</t>
+          <t>155055</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>207773</t>
+          <t>206130</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3228267</t>
+          <t>3229859</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3251746</t>
+          <t>3252419</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3210105</t>
+          <t>3209321</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3258051</t>
+          <t>3257656</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6447968</t>
+          <t>6449611</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6502027</t>
+          <t>6500686</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,67%</t>
         </is>
       </c>
     </row>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12110</t>
+          <t>13117</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>91565</t>
+          <t>89370</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>130198</t>
+          <t>130863</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>93070</t>
+          <t>92236</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>135491</t>
+          <t>135237</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>961530</t>
+          <t>960523</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1206490</t>
+          <t>1205825</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1245123</t>
+          <t>1247318</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2174837</t>
+          <t>2175091</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2217258</t>
+          <t>2218092</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,01%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>984</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8185</t>
+          <t>9062</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15706</t>
+          <t>15628</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35898</t>
+          <t>36956</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18748</t>
+          <t>18551</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39763</t>
+          <t>40603</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1955772</t>
+          <t>1954895</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1962974</t>
+          <t>1962973</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1718694</t>
+          <t>1717636</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1738886</t>
+          <t>1738964</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3678786</t>
+          <t>3677946</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3699801</t>
+          <t>3699998</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3837</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17185</t>
+          <t>17400</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>3788</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18119</t>
+          <t>17887</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>441446</t>
+          <t>441231</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>454966</t>
+          <t>454794</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>921694</t>
+          <t>921926</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>936094</t>
+          <t>936025</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2057</t>
+          <t>2085</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16052</t>
+          <t>16256</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>119193</t>
+          <t>118998</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>169762</t>
+          <t>167194</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>126669</t>
+          <t>127505</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>175391</t>
+          <t>179078</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3402727</t>
+          <t>3402523</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3416722</t>
+          <t>3416694</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3380149</t>
+          <t>3382717</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3430718</t>
+          <t>3430913</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6793299</t>
+          <t>6789612</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6842021</t>
+          <t>6841185</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,17%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1695</t>
+          <t>1643</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10545</t>
+          <t>10790</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>53025</t>
+          <t>50749</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>87091</t>
+          <t>84474</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>56151</t>
+          <t>56373</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>89966</t>
+          <t>92308</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>743802</t>
+          <t>743557</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>752652</t>
+          <t>752704</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>907569</t>
+          <t>910186</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>941635</t>
+          <t>943911</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1659041</t>
+          <t>1656699</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1692856</t>
+          <t>1692634</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,78%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1829</t>
+          <t>1666</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10858</t>
+          <t>11210</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32426</t>
+          <t>31952</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60022</t>
+          <t>59670</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35986</t>
+          <t>35117</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>64904</t>
+          <t>65428</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2065527</t>
+          <t>2065175</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2074556</t>
+          <t>2074719</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1928278</t>
+          <t>1928630</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1955874</t>
+          <t>1956348</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3999781</t>
+          <t>3999257</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4028699</t>
+          <t>4029568</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7342</t>
+          <t>7197</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5194</t>
+          <t>5027</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18560</t>
+          <t>19124</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6500</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23182</t>
+          <t>21747</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>539544</t>
+          <t>539689</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>530580</t>
+          <t>530016</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>543946</t>
+          <t>544113</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1072845</t>
+          <t>1074280</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1089527</t>
+          <t>1089753</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,43%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5914</t>
+          <t>6128</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19918</t>
+          <t>19958</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>100033</t>
+          <t>102632</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>144158</t>
+          <t>146070</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>110567</t>
+          <t>111611</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>159455</t>
+          <t>158800</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3357700</t>
+          <t>3357660</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3371704</t>
+          <t>3371490</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3387942</t>
+          <t>3386030</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3432067</t>
+          <t>3429468</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6750263</t>
+          <t>6750918</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6799151</t>
+          <t>6798107</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,38%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>11420</t>
+          <t>12033</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6931</t>
+          <t>7406</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16998</t>
+          <t>19355</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,27 +5572,27 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>86153</t>
+          <t>94524</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>73700</t>
+          <t>80843</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>99230</t>
+          <t>108239</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>97573</t>
+          <t>106557</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>84581</t>
+          <t>92774</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>111128</t>
+          <t>122479</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>498770</t>
+          <t>561528</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>493192</t>
+          <t>554206</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>503259</t>
+          <t>566155</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,22 +5685,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>662760</t>
+          <t>722217</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>649683</t>
+          <t>708502</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>675213</t>
+          <t>735898</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1161530</t>
+          <t>1283745</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1147975</t>
+          <t>1267823</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1174522</t>
+          <t>1297528</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,33%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>510190</t>
+          <t>573561</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>510190</t>
+          <t>573561</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>510190</t>
+          <t>573561</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>748913</t>
+          <t>816741</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>748913</t>
+          <t>816741</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>748913</t>
+          <t>816741</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1259103</t>
+          <t>1390302</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1259103</t>
+          <t>1390302</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1259103</t>
+          <t>1390302</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14413</t>
+          <t>14892</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7251</t>
+          <t>7568</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30574</t>
+          <t>27772</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>55997</t>
+          <t>61269</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38291</t>
+          <t>49825</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>71079</t>
+          <t>75471</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>70409</t>
+          <t>76161</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53989</t>
+          <t>62633</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>89961</t>
+          <t>96380</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2274678</t>
+          <t>2214308</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2258517</t>
+          <t>2201428</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2281840</t>
+          <t>2221632</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2175573</t>
+          <t>2103192</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2160491</t>
+          <t>2088990</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2193279</t>
+          <t>2114636</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4450253</t>
+          <t>4317501</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4430701</t>
+          <t>4297282</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4466673</t>
+          <t>4331029</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,57%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2289091</t>
+          <t>2229200</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2289091</t>
+          <t>2229200</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2289091</t>
+          <t>2229200</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2231570</t>
+          <t>2164461</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2231570</t>
+          <t>2164461</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2231570</t>
+          <t>2164461</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4520662</t>
+          <t>4393662</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4520662</t>
+          <t>4393662</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4520662</t>
+          <t>4393662</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2484</t>
+          <t>2582</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>859</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>6464</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>16963</t>
+          <t>19617</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11484</t>
+          <t>14198</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23208</t>
+          <t>27468</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>19447</t>
+          <t>22198</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13347</t>
+          <t>15426</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26186</t>
+          <t>30430</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>643090</t>
+          <t>707876</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>639041</t>
+          <t>703994</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>644839</t>
+          <t>709599</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>99,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>641914</t>
+          <t>712434</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>635669</t>
+          <t>704583</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>647393</t>
+          <t>717853</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1285004</t>
+          <t>1420311</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1278265</t>
+          <t>1412079</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1291104</t>
+          <t>1427083</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>645574</t>
+          <t>710458</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>645574</t>
+          <t>710458</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>645574</t>
+          <t>710458</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>658877</t>
+          <t>732051</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>658877</t>
+          <t>732051</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>658877</t>
+          <t>732051</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1304451</t>
+          <t>1442509</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1304451</t>
+          <t>1442509</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1304451</t>
+          <t>1442509</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,22 +6566,22 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>28317</t>
+          <t>29507</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19125</t>
+          <t>19568</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46243</t>
+          <t>44761</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>159113</t>
+          <t>175410</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>130966</t>
+          <t>154720</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>182774</t>
+          <t>195350</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>187430</t>
+          <t>204917</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>159239</t>
+          <t>183281</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>214130</t>
+          <t>229287</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -6679,27 +6679,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3416538</t>
+          <t>3483713</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3398612</t>
+          <t>3468459</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3425730</t>
+          <t>3493652</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3480247</t>
+          <t>3537843</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3456586</t>
+          <t>3517903</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3508394</t>
+          <t>3558533</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6896785</t>
+          <t>7021556</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6870085</t>
+          <t>6997186</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6924976</t>
+          <t>7043192</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,46%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3444855</t>
+          <t>3513220</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3444855</t>
+          <t>3513220</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3444855</t>
+          <t>3513220</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3639360</t>
+          <t>3713253</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3639360</t>
+          <t>3713253</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3639360</t>
+          <t>3713253</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7084215</t>
+          <t>7226473</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7084215</t>
+          <t>7226473</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7084215</t>
+          <t>7226473</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
